--- a/CQ_Generation_Framework/output/joint_filtered_cqs_20260722_174443.xlsx
+++ b/CQ_Generation_Framework/output/joint_filtered_cqs_20260722_174443.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What categories of radiation treatment protocols are defined in preclinical studies?</t>
+          <t>What categories of intervention procedures are employed in preclinical studies?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -476,21 +476,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What relationships exist between the named model characteristics and treatment outcomes in radiation oncology research?</t>
+          <t>What properties characterize the laboratory measurements taken during the named trials?</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
       <c r="E3" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -504,17 +504,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What properties describe the data annotation process for experimental findings in the named field?</t>
+          <t>What components constitute a comprehensive intervention procedure in preclinical trials?</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="E4" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -524,21 +524,21 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What properties characterize the subject characteristics in preclinical trials in radiation oncology?</t>
+          <t>What types of laboratory measurements are utilized to quantify growth inhibition after treatment?</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="E5" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -548,21 +548,21 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What types of biological models are used in preclinical trials for radiation oncology?</t>
+          <t>What types of intervention procedures are associated with enhanced response rates in trials?</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -572,21 +572,21 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What relationships exist between treatment protocols and observed outcomes in named studies?</t>
+          <t>What types of laboratory measurements correlate with named outcomes after treatment interventions?</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="E7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -596,21 +596,21 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What criteria define the experimental design of preclinical trials in the named field?</t>
+          <t>What properties define the demographics of subjects used in preclinical radiation trials?</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="E8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -620,21 +620,21 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What types of experimental designs are employed to evaluate combination therapies involving the named treatment modalities?</t>
+          <t>What properties define the variables measured during laboratory assessments in preclinical evaluations?</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="E9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -644,21 +644,21 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What types of laboratory findings are commonly reported in preclinical trials involving the named treatment modality?</t>
+          <t>What properties describe the characteristics of intervention procedures used in named studies?</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="E10" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -668,21 +668,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological environment characteristics and treatment responses observed in preclinical studies?</t>
+          <t>What properties characterize the cohort descriptions used in preclinical trials for data analysis?</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="E11" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -692,21 +692,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What categories of outcome measures are prioritized when evaluating named adverse effects associated with named treatment protocols?</t>
+          <t>What criteria are used to evaluate the effectiveness of different intervention procedures in trials?</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="E12" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -716,21 +716,21 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What criteria define the success of a treatment protocol in achieving named outcome during preclinical trials?</t>
+          <t>What criteria define the inclusion and exclusion of subjects in preclinical trials?</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="E13" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -740,21 +740,21 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What outcome measures are utilized to assess the efficacy of named treatments in preclinical studies?</t>
+          <t>What types of biological models are utilized in preclinical trials for radiation oncology?</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="E14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -764,21 +764,21 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What types of outcome measurements are used to evaluate the effectiveness of new interventions in preclinical trials?</t>
+          <t>What types of data integration methods are applied in preclinical research in the named field?</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What types of knowledge representations can be developed to facilitate semantic interoperability among diverse datasets in radiation oncology research?</t>
+          <t>What criteria are used to classify healthy tissue responses to radiation in the named models?</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="E16" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What relationships exist between genetic alterations and local-regional control outcomes following radiation treatment in cancer models?</t>
+          <t>What categories of intervention procedures have been shown to minimize collateral damage to healthy tissues?</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="E17" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -836,21 +836,21 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What components constitute a standardized framework for reporting outcomes from preclinical trials in the named field?</t>
+          <t>What relationships exist between intervention timing and outcomes observed in preclinical studies?</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="E18" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -860,21 +860,21 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What criteria define successful integration practices for combining datasets from multiple sources within the named field?</t>
+          <t>What relationships exist between intervention procedures and observed outcomes in the named models?</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="E19" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -884,21 +884,21 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological effects and treatment outcomes in preclinical trials with named therapy?</t>
+          <t>What types of laboratory measurements are critical for assessing named toxicity in preclinical trials?</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What categories of semantic interoperability challenges are faced in integrating data from multiple studies in the named field?</t>
+          <t>What types of clinical observations are recorded during preclinical trials in the named field?</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.62</v>
+        <v>0.49</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -932,21 +932,21 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What properties define the criteria for selecting appropriate biological models for specific types of oncology research involving radiation treatment?</t>
+          <t>What properties describe the laboratory measurements related to named biological response in preclinical research?</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E22" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -956,21 +956,21 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What relationships exist between treatment timing and efficacy when combining the named therapy with the named therapy protocols in preclinical studies?</t>
+          <t>What categories of clinical observations are relevant to assessing treatment efficacy in preclinical studies?</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.71</v>
+        <v>0.49</v>
       </c>
       <c r="E23" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -980,21 +980,21 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What relationships exist between the named demographics and treatment outcomes observed across different trial phases?</t>
+          <t>What types of data standards are utilized for sharing experimental data in the named field?</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What relationships exist between treatment duration and overall survival rates noted among subjects participating across various trial phases involving novel interventions derived from prior investigations conducted using preclinical models as part thereof?</t>
+          <t>What categories of laboratory measurements are essential for evaluating treatment effects on the named biological entities?</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1028,21 +1028,21 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What types of data sharing practices are implemented among entities conducting preclinical trials?</t>
+          <t>What types of data annotation practices are employed for experimental data in this type of research?</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1052,21 +1052,21 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What properties describe the mechanisms underlying the named effect observed in radiation oncology studies?</t>
+          <t>What relationships exist between dose escalation protocols and observed toxicity levels in preclinical models?</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1076,21 +1076,21 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What properties define the structure and content requirements for annotated datasets used within this field?</t>
+          <t>What categories of healthy tissue measurements are taken to assess the side effects of the named treatment?</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What categories of data integration methods are applied in preclinical research in the named field?</t>
+          <t>What relationships exist between intervention procedures and recovery times observed post-treatment?</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What categories of data annotation standards are used to ensure consistency across different studies in this field?</t>
+          <t>What types of experimental data are collected from biological models treated with the named therapy?</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="E30" t="n">
-        <v>0.67</v>
+        <v>0.84</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1152,17 +1152,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What types of biomarkers are measured as part of outcome assessments in preclinical therapy research?</t>
+          <t>What types of clinical observations indicate adverse effects on healthy tissue during the named treatment?</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="E31" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What relationships exist between specific biomarker expressions and treatment responses observed following combined therapies?</t>
+          <t>What relationships exist between specific interventions and their impact on named biological indicators post-treatment?</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E32" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What categories of data integration techniques enhance the analysis of results from multiple named studies?</t>
+          <t>What criteria determine the assessment endpoints for the named models undergoing radiation treatment?</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>0.51</v>
+        <v>0.33</v>
       </c>
       <c r="E33" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1220,21 +1220,21 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What categories of named biological models are utilized for drug testing and evaluation in radiation oncology research?</t>
+          <t>What criteria define successful tumor control following various treatment modalities?</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="E34" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1244,21 +1244,21 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What types of experimental controls are necessary to ensure valid comparisons within treatment groups during trials?</t>
+          <t>What categories of healthy tissue assessments are necessary for evaluating treatment safety profiles?</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.55</v>
+        <v>0.36</v>
       </c>
       <c r="E35" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What categories of experimental data are collected during preclinical trials involving named therapeutic techniques?</t>
+          <t>What categories of data sharing practices facilitate collaboration among researchers in the named field?</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="E36" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological models and their translational relevance to named medical treatments?</t>
+          <t>What criteria determine which variables should be monitored during observations in trials?</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="E37" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What types of computational tools can be utilized to facilitate data integration across various platforms within the named research field?</t>
+          <t>What types of data annotation standards improve reproducibility in preclinical trial reporting?</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="E38" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1340,21 +1340,21 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What categories of translational research strategies can be derived from findings obtained through named models in radiation oncology?</t>
+          <t>What categories of data integration techniques enhance the analysis of named trial results?</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.58</v>
+        <v>0.38</v>
       </c>
       <c r="E39" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1364,21 +1364,21 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What relationships exist between specific patient characteristics and their likelihood to experience adverse reactions during treatment regimens?</t>
+          <t>What properties characterize the named biological entities studied in preclinical radiation oncology trials?</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="E40" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1388,21 +1388,21 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What properties define successful strategies for enhancing reproducibility across diverse experimental designs within this domain?</t>
+          <t>What properties characterize the measurement techniques used to evaluate tissue damage from the named exposure?</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="E41" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1412,21 +1412,21 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What components constitute a standardized protocol for documenting findings across multiple institutions conducting similar experiments?</t>
+          <t>What properties describe the methodologies used for conducting observations in trials?</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.6</v>
+        <v>0.42</v>
       </c>
       <c r="E42" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1436,21 +1436,21 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What types of observational studies are conducted to assess outcomes related to the named intervention in the named models?</t>
+          <t>What properties define the characteristics of cohorts selected for specific disease type studies?</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="E43" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1460,21 +1460,21 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What criteria are used to classify different types of adverse events observed during preclinical trials in radiation therapy?</t>
+          <t>What criteria determine the standardization processes for experimental data across different studies?</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.63</v>
+        <v>0.42</v>
       </c>
       <c r="E44" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What properties characterize the methodologies used for assessing biological responses following named treatments in named models?</t>
+          <t>What relationships exist between circulating biomarker levels and tumor response to radiation therapy?</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
       <c r="E45" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1508,21 +1508,21 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological characteristics and response rates observed during clinical evaluations post-preclinical findings?</t>
+          <t>What types of data integration methods enhance comparative analyses across multiple named studies?</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="E46" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What types of statistical analyses are performed to assess the significance of findings from experimental designs in preclinical studies?</t>
+          <t>What relationships exist between cohort descriptions and the outcomes of named therapy studies?</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="E47" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1556,21 +1556,21 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What components make up a comprehensive database for storing experimental data from multiple research facilities conducting preclinical research?</t>
+          <t>What relationships exist between specific subject demographics and treatment outcomes in studies?</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>0.67</v>
+        <v>0.45</v>
       </c>
       <c r="E48" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1584,41 +1584,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What types of imaging techniques are employed to monitor treatment responses during preclinical trials in radiation therapy?</t>
+          <t>What categories of clinical observations are necessary for understanding named biological model responses?</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What types of statistical methods are applied to analyze outcome measures across different experimental frameworks?</t>
+          <t>What types of cohort descriptions provide insights into variability affecting treatment outcomes?</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1628,45 +1628,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What components constitute a comprehensive assessment framework for evaluating long-term outcomes following the named treatment?</t>
+          <t>What categories of laboratory measurements assess cellular responses to different named modalities?</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What components make up an effective reporting standard for documenting laboratory findings from named trials?</t>
+          <t>What relationships exist between the named techniques and the named observations during treatment evaluation?</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological markers levels and tumor burden during named treatment cycles?</t>
+          <t>What relationships exist between named biological response and named treatment parameter in preclinical studies?</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1700,429 +1700,429 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What types of adverse effects should be monitored as part of toxicity assessments during named therapy studies?</t>
+          <t>What relationships exist between the named analysis and observed responses to various therapeutic interventions?</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="E54" t="n">
-        <v>0.49</v>
+        <v>0.67</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What properties define the validation process for new indicators identified through experimental designs in disease research?</t>
+          <t>What criteria define acceptable thresholds for adverse effects observed during named observations?</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="E55" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What types of observational metrics should be prioritized when assessing quality-of-life impacts resulting from various treatment approaches?</t>
+          <t>What types of laboratory measurements inform on long-term effects post-named treatment?</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E56" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What components make up a robust methodology for evaluating systemic effects resulting from localized treatment modalities?</t>
+          <t>What types of clinical observations provide evidence for the named effect following localized treatments?</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>0.48</v>
+        <v>0.66</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What properties define the named data structures used to represent data from preclinical trials in the named field?</t>
+          <t>What criteria guide the selection of appropriate biological models for specific research questions in oncology?</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="E58" t="n">
-        <v>0.47</v>
+        <v>0.66</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What relationships exist between dose escalation protocols and observed toxicities during clinical evaluations following named studies?</t>
+          <t>What categories of intervention procedures have shown promise in enhancing named biological responses alongside named treatment?</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="E59" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What categories define best practices for documenting experimental procedures within the named submissions related to the named studies?</t>
+          <t>What relationships exist between the named factors and their influence on experimental outcomes observed across multiple groups?</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="E60" t="n">
-        <v>0.45</v>
+        <v>0.64</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What components constitute a robust framework for ensuring named principles are adhered to during data sharing among named entities?</t>
+          <t>What properties define the named biological environment assessed during preclinical radiation studies?</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="E61" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What criteria determine the classification of different adverse events related to the named therapy combined with the named treatment?</t>
+          <t>What types of intervention procedures have been associated with improved outcomes in clinical settings?</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.67</v>
+        <v>0.45</v>
       </c>
       <c r="E62" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What categories of methodological approaches can be utilized to improve translational relevance when moving from laboratory to clinical applications?</t>
+          <t>What categories of data integration frameworks support analysis across multiple named studies?</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>0.66</v>
+        <v>0.42</v>
       </c>
       <c r="E63" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What types of safety assessments should be included as part of routine evaluations during early-phase trials following promising preclinical results?</t>
+          <t>What categories of clinical observations help identify biomarkers predictive of treatment response?</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.72</v>
+        <v>0.44</v>
       </c>
       <c r="E64" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What types of analytical methods can be employed to assess correlations between named biological indicators and named clinical outcomes observed during follow-up evaluations post-treatment initiation?</t>
+          <t>What categories of data integration strategies facilitate real-time analysis during ongoing experiments?</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
       <c r="E65" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What properties characterize effective communication strategies for disseminating findings from collaborative research efforts?</t>
+          <t>What properties characterize the experimental designs used to assess combination therapies involving the named treatment modality?</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="E66" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What categories of knowledge representation techniques support semantic interoperability across various named databases?</t>
+          <t>What properties describe the methodologies employed for accurate measurement reporting during experiments?</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>0.46</v>
       </c>
       <c r="E67" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What categories of ethical guidelines must be followed when designing experiments involving named subjects?</t>
+          <t>What relationships exist between named biological populations and their response to named treatment?</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E68" t="n">
         <v>0.5</v>
       </c>
-      <c r="E68" t="n">
-        <v>0.15</v>
-      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What properties characterize effective communication channels established among multidisciplinary teams working on complex research projects?</t>
+          <t>What properties define optimal conditions for conducting laboratory measurements related to named assessments?</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="E69" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What categories of collaborative frameworks can enhance data sharing practices among researchers conducting similar studies?</t>
+          <t>What properties characterize standardized protocols necessary for ensuring reproducibility within named trial frameworks?</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="E70" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What categories of named profiling techniques can be employed to assess named characteristics prior to initiating therapy?</t>
+          <t>What types of laboratory measurements assess immune response following named treatment in subjects?</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="E71" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2132,21 +2132,21 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What properties characterize the ethical considerations involved in conducting experiments on named subjects for radiation oncology research?</t>
+          <t>What types of clinical observations contribute to understanding long-term survivorship issues post-intervention?</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="E72" t="n">
-        <v>0.12</v>
+        <v>0.49</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What properties characterize effective training programs aimed at improving understanding among stakeholders regarding named principles?</t>
+          <t>What relationships exist between named biological factors and therapeutic efficacy observed in trials?</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="E73" t="n">
-        <v>0.12</v>
+        <v>0.49</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2180,21 +2180,21 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What components make up an effective feedback mechanism for participants involved in collaborative projects focused on shared objectives?</t>
+          <t>What criteria determine which named demographics yield the most relevant results for named applications?</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="E74" t="n">
-        <v>0.1</v>
+        <v>0.48</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What components constitute an effective framework for evaluating potential biases that may arise during data collection processes across different research environments?</t>
+          <t>What properties characterize effective data sharing platforms for collaborative research efforts?</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="E75" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What properties define successful strategies aimed at ensuring ethical compliance throughout all stages involved within translational research initiatives focused on named therapies?</t>
+          <t>What relationships exist between the named conditions and reproducibility rates observed across studies?</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0.84</v>
+        <v>0.45</v>
       </c>
       <c r="E76" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2256,17 +2256,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What categories encompass key performance indicators utilized when measuring success rates achieved through implementation efforts surrounding innovative therapeutic approaches developed via rigorous scientific inquiry?</t>
+          <t>What criteria guide the development and validation processes for new measurement tools used in experiments?</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.89</v>
+        <v>0.45</v>
       </c>
       <c r="E77" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>What components comprise an optimal set-up necessary for conducting high-quality systematic reviews aimed at synthesizing evidence gathered through diverse lines-of-inquiry pertaining specifically towards advancements made within this named discipline?</t>
+          <t>What properties characterize successful collaborations among named teams conducting research?</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2300,23 +2300,47 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What types encompass essential elements required while formulating comprehensive guidelines intended towards promoting transparency &amp; reproducibility standards adhered-to by investigators engaged-in similar lines-of-research?</t>
+          <t>What properties define effective communication strategies among stakeholders involved in named research projects?</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>68</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>What criteria guide ethical considerations when selecting named models for preclinical research?</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
         <v>1</v>
       </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="D80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2333,7 +2357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2351,600 +2375,828 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Radiation Treatment Protocols</t>
+          <t>Intervention Procedures</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What categories of radiation treatment protocols are defined in preclinical studies?</t>
+          <t>What categories of intervention procedures are employed in preclinical studies?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Radiation Treatment Protocols</t>
+          <t>Intervention Procedures</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What relationships exist between treatment protocols and observed outcomes in named studies?</t>
+          <t>What components constitute a comprehensive intervention procedure in preclinical trials?</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Radiation Treatment Protocols</t>
+          <t>Intervention Procedures</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What criteria define the success of a treatment protocol in achieving named outcome during preclinical trials?</t>
+          <t>What types of intervention procedures are associated with enhanced response rates in trials?</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Radiation Treatment Protocols</t>
+          <t>Intervention Procedures</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What relationships exist between treatment timing and efficacy when combining the named therapy with the named therapy protocols in preclinical studies?</t>
+          <t>What categories of intervention procedures have been shown to minimize collateral damage to healthy tissues?</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Radiation Treatment Protocols</t>
+          <t>Intervention Procedures</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What relationships exist between treatment duration and overall survival rates noted among subjects participating across various trial phases involving novel interventions derived from prior investigations conducted using preclinical models as part thereof?</t>
+          <t>What types of intervention procedures have been associated with improved outcomes in clinical settings?</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Biological Models and Characteristics</t>
+          <t>Intervention Procedures</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What types of biological models are used in preclinical trials for radiation oncology?</t>
+          <t>What categories of intervention procedures have shown promise in enhancing named biological responses alongside named treatment?</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Biological Models and Characteristics</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What properties characterize the subject characteristics in preclinical trials in radiation oncology?</t>
+          <t>What properties characterize the laboratory measurements taken during the named trials?</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biological Models and Characteristics</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological models and their translational relevance to named medical treatments?</t>
+          <t>What types of laboratory measurements are utilized to quantify growth inhibition after treatment?</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biological Models and Characteristics</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What properties define the criteria for selecting appropriate biological models for specific types of oncology research involving radiation treatment?</t>
+          <t>What types of laboratory measurements correlate with named outcomes after treatment interventions?</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biological Models and Characteristics</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What categories of named biological models are utilized for drug testing and evaluation in radiation oncology research?</t>
+          <t>What properties define the variables measured during laboratory assessments in preclinical evaluations?</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Annotation and Integration</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What properties describe the data annotation process for experimental findings in the named field?</t>
+          <t>What types of laboratory measurements are critical for assessing named toxicity in preclinical trials?</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Annotation and Integration</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What properties define the structure and content requirements for annotated datasets used within this field?</t>
+          <t>What categories of laboratory measurements are essential for evaluating treatment effects on the named biological entities?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Annotation and Integration</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What categories of data annotation standards are used to ensure consistency across different studies in this field?</t>
+          <t>What categories of laboratory measurements assess cellular responses to different named modalities?</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Annotation and Integration</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What categories of data integration methods are applied in preclinical research in the named field?</t>
+          <t>What types of laboratory measurements inform on long-term effects post-named treatment?</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Annotation and Integration</t>
+          <t>Laboratory Measurements</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What categories of data integration techniques enhance the analysis of results from multiple named studies?</t>
+          <t>What properties define optimal conditions for conducting laboratory measurements related to named assessments?</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Annotation and Integration</t>
+          <t>Subject Demographics and Cohorts</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What types of computational tools can be utilized to facilitate data integration across various platforms within the named research field?</t>
+          <t>What properties define the demographics of subjects used in preclinical radiation trials?</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Outcome Measures and Efficacy</t>
+          <t>Subject Demographics and Cohorts</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What categories of outcome measures are prioritized when evaluating named adverse effects associated with named treatment protocols?</t>
+          <t>What properties characterize the cohort descriptions used in preclinical trials for data analysis?</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Outcome Measures and Efficacy</t>
+          <t>Subject Demographics and Cohorts</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What outcome measures are utilized to assess the efficacy of named treatments in preclinical studies?</t>
+          <t>What criteria define the inclusion and exclusion of subjects in preclinical trials?</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Outcome Measures and Efficacy</t>
+          <t>Subject Demographics and Cohorts</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What types of outcome measurements are used to evaluate the effectiveness of new interventions in preclinical trials?</t>
+          <t>What properties define the characteristics of cohorts selected for specific disease type studies?</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Outcome Measures and Efficacy</t>
+          <t>Subject Demographics and Cohorts</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What types of biomarkers are measured as part of outcome assessments in preclinical therapy research?</t>
+          <t>What types of cohort descriptions provide insights into variability affecting treatment outcomes?</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Outcome Measures and Efficacy</t>
+          <t>Subject Demographics and Cohorts</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What relationships exist between specific biomarker expressions and treatment responses observed following combined therapies?</t>
+          <t>What relationships exist between specific subject demographics and treatment outcomes in studies?</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Outcome Measures and Efficacy</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological markers levels and tumor burden during named treatment cycles?</t>
+          <t>What types of data integration methods are applied in preclinical research in the named field?</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Experimental Design and Methodologies</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What criteria define the experimental design of preclinical trials in the named field?</t>
+          <t>What types of data standards are utilized for sharing experimental data in the named field?</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Experimental Design and Methodologies</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What types of experimental designs are employed to evaluate combination therapies involving the named treatment modalities?</t>
+          <t>What categories of data sharing practices facilitate collaboration among researchers in the named field?</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Experimental Design and Methodologies</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What types of experimental controls are necessary to ensure valid comparisons within treatment groups during trials?</t>
+          <t>What types of data annotation practices are employed for experimental data in this type of research?</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Experimental Design and Methodologies</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What properties characterize the methodologies used for assessing biological responses following named treatments in named models?</t>
+          <t>What types of data annotation standards improve reproducibility in preclinical trial reporting?</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Experimental Design and Methodologies</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What types of statistical analyses are performed to assess the significance of findings from experimental designs in preclinical studies?</t>
+          <t>What categories of data integration techniques enhance the analysis of named trial results?</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Experimental Design and Methodologies</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What types of statistical methods are applied to analyze outcome measures across different experimental frameworks?</t>
+          <t>What categories of data integration frameworks support analysis across multiple named studies?</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Challenges and Best Practices</t>
+          <t>Data Integration and Standards</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What categories of semantic interoperability challenges are faced in integrating data from multiple studies in the named field?</t>
+          <t>What categories of data integration strategies facilitate real-time analysis during ongoing experiments?</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Challenges and Best Practices</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What criteria define successful integration practices for combining datasets from multiple sources within the named field?</t>
+          <t>What criteria are used to evaluate the effectiveness of different intervention procedures in trials?</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Challenges and Best Practices</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What properties define successful strategies for enhancing reproducibility across diverse experimental designs within this domain?</t>
+          <t>What relationships exist between intervention procedures and observed outcomes in the named models?</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Challenges and Best Practices</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What components constitute a standardized framework for reporting outcomes from preclinical trials in the named field?</t>
+          <t>What relationships exist between intervention timing and outcomes observed in preclinical studies?</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Challenges and Best Practices</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What components make up an effective reporting standard for documenting laboratory findings from named trials?</t>
+          <t>What criteria determine the assessment endpoints for the named models undergoing radiation treatment?</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Patient and Demographic Factors</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What relationships exist between the named demographics and treatment outcomes observed across different trial phases?</t>
+          <t>What criteria define successful tumor control following various treatment modalities?</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Patient and Demographic Factors</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What relationships exist between specific patient characteristics and their likelihood to experience adverse reactions during treatment regimens?</t>
+          <t>What relationships exist between circulating biomarker levels and tumor response to radiation therapy?</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Patient and Demographic Factors</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological effects and treatment outcomes in preclinical trials with named therapy?</t>
+          <t>What categories of clinical observations are necessary for understanding named biological model responses?</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Patient and Demographic Factors</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What relationships exist between genetic alterations and local-regional control outcomes following radiation treatment in cancer models?</t>
+          <t>What categories of clinical observations help identify biomarkers predictive of treatment response?</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Patient and Demographic Factors</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological characteristics and response rates observed during clinical evaluations post-preclinical findings?</t>
+          <t>What relationships exist between specific interventions and their impact on named biological indicators post-treatment?</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Treatment Efficacy and Outcomes</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What types of data sharing practices are implemented among entities conducting preclinical trials?</t>
+          <t>What relationships exist between the named factors and their influence on experimental outcomes observed across multiple groups?</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Toxicity and Safety Assessments</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What relationships exist between the named model characteristics and treatment outcomes in radiation oncology research?</t>
+          <t>What categories of healthy tissue measurements are taken to assess the side effects of the named treatment?</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Toxicity and Safety Assessments</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What types of observational studies are conducted to assess outcomes related to the named intervention in the named models?</t>
+          <t>What types of clinical observations indicate adverse effects on healthy tissue during the named treatment?</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Toxicity and Safety Assessments</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What relationships exist between named biological environment characteristics and treatment responses observed in preclinical studies?</t>
+          <t>What categories of healthy tissue assessments are necessary for evaluating treatment safety profiles?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Toxicity and Safety Assessments</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What types of laboratory findings are commonly reported in preclinical trials involving the named treatment modality?</t>
+          <t>What criteria define acceptable thresholds for adverse effects observed during named observations?</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Toxicity and Safety Assessments</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What types of knowledge representations can be developed to facilitate semantic interoperability among diverse datasets in radiation oncology research?</t>
+          <t>What relationships exist between dose escalation protocols and observed toxicity levels in preclinical models?</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Toxicity and Safety Assessments</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What properties describe the mechanisms underlying the named effect observed in radiation oncology studies?</t>
+          <t>What relationships exist between intervention procedures and recovery times observed post-treatment?</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Methodologies and Experimental Design</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What components make up a comprehensive database for storing experimental data from multiple research facilities conducting preclinical research?</t>
+          <t>What properties describe the methodologies used for conducting observations in trials?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Methodologies and Experimental Design</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What categories of translational research strategies can be derived from findings obtained through named models in radiation oncology?</t>
+          <t>What properties characterize the measurement techniques used to evaluate tissue damage from the named exposure?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Methodologies and Experimental Design</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What components constitute a standardized protocol for documenting findings across multiple institutions conducting similar experiments?</t>
+          <t>What properties characterize the experimental designs used to assess combination therapies involving the named treatment modality?</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Methodologies and Experimental Design</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What categories of experimental data are collected during preclinical trials involving named therapeutic techniques?</t>
+          <t>What properties describe the methodologies employed for accurate measurement reporting during experiments?</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Methodologies and Experimental Design</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>What properties define the named biological environment assessed during preclinical radiation studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Methodologies and Experimental Design</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>What relationships exist between named biological populations and their response to named treatment?</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Methodologies and Experimental Design</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>What relationships exist between the named analysis and observed responses to various therapeutic interventions?</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>What criteria are used to classify different types of adverse events observed during preclinical trials in radiation therapy?</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>What criteria guide the selection of appropriate biological models for specific research questions in oncology?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>What properties characterize standardized protocols necessary for ensuring reproducibility within named trial frameworks?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>What criteria determine which variables should be monitored during observations in trials?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>What properties describe the characteristics of intervention procedures used in named studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>What criteria determine the standardization processes for experimental data across different studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>What types of experimental data are collected from biological models treated with the named therapy?</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>What categories of clinical observations are relevant to assessing treatment efficacy in preclinical studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>What types of data integration methods enhance comparative analyses across multiple named studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>What properties characterize the named biological entities studied in preclinical radiation oncology trials?</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>What types of clinical observations are recorded during preclinical trials in the named field?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>What relationships exist between cohort descriptions and the outcomes of named therapy studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>What relationships exist between the named techniques and the named observations during treatment evaluation?</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>What properties describe the laboratory measurements related to named biological response in preclinical research?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>What criteria are used to classify healthy tissue responses to radiation in the named models?</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>What relationships exist between named biological response and named treatment parameter in preclinical studies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>What types of biological models are utilized in preclinical trials for radiation oncology?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>What types of clinical observations provide evidence for the named effect following localized treatments?</t>
         </is>
       </c>
     </row>
@@ -2959,7 +3211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2992,50 +3244,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[7, 12]</t>
+          <t>[31, 71]</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[12]</t>
+          <t>[71]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>What criteria define the experimental design of preclinical trials in the named field?</t>
+          <t>What categories of healthy tissue measurements are taken to assess the side effects of the named treatment?</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['What components constitute a comprehensive experimental design for preclinical trials in the named field?']</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>[57, 67]</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>57</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[67]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>What relationships exist between named biological characteristics and response rates observed during clinical evaluations post-preclinical findings?</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['What relationships exist between specific biological indicators and therapeutic responses observed during clinical evaluations post-preclinical investigations?']</t>
+          <t>['What categories of healthy tissue evaluations inform best practices for minimizing side effects during the named treatment?']</t>
         </is>
       </c>
     </row>
